--- a/100 days of code/Day_32/birthday.xlsx
+++ b/100 days of code/Day_32/birthday.xlsx
@@ -415,7 +415,7 @@
         <v>Jai Singh Rajput</v>
       </c>
       <c r="B2" t="str">
-        <v>21-10</v>
+        <v>02-04</v>
       </c>
       <c r="C2" t="str">
         <v>jai.s.rajput.dev@gmail.com</v>
